--- a/data/chinese/P2T3_Chapter20.xlsx
+++ b/data/chinese/P2T3_Chapter20.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408EB4B3-B065-F649-B7A1-C78900AE8DB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58E3B6F-44E7-5E4C-BAD1-6D82842FBDD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,46 +60,51 @@
     <t>咕咚</t>
   </si>
   <si>
-    <t>模擬重物墜落、墜入水中的聲音</t>
-  </si>
-  <si>
     <t>成熟的木瓜從樹上掉下，咕咚一聲掉進湖裡。</t>
   </si>
   <si>
     <t>逃命</t>
   </si>
   <si>
-    <t>遇見危險時趕緊逃跑保全性命</t>
-  </si>
-  <si>
     <t>野獸看見獵人，紛紛往山林深處逃命。</t>
   </si>
   <si>
     <t>熱鬧</t>
   </si>
   <si>
-    <t>人多聲雜，場面十分喧騰歡快</t>
-  </si>
-  <si>
     <t>集市上人來人往，顯得非常熱鬧。</t>
   </si>
   <si>
     <t>拔腿就跑</t>
   </si>
   <si>
-    <t>立刻邁開腳快速逃走</t>
-  </si>
-  <si>
     <t>看見突然竄出的大狗，他嚇得拔腿就跑。</t>
   </si>
   <si>
     <t>嚇了一跳</t>
   </si>
   <si>
-    <t>突如其來的事物使人受到驚訝</t>
-  </si>
-  <si>
     <t>身後突然傳來大喊聲，讓我嚇了一跳。</t>
+  </si>
+  <si>
+    <t>形容東西掉進水裡或落地的聲音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遇到危險時趕快跑開，保住自己的性命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人很多、聲音很吵，很熱鬧的樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>趕快邁開腳跑走，形容跑得很快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被突然發生的事驚嚇到，嚇了一大跳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -778,7 +783,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="53.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -813,10 +818,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -825,13 +830,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -840,13 +845,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -855,13 +860,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -870,13 +875,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
